--- a/ci-build/StructureDefinition-ex-senologie-pre-op-blutabnahme.xlsx
+++ b/ci-build/StructureDefinition-ex-senologie-pre-op-blutabnahme.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="106">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T14:42:03+00:00</t>
+    <t>2026-10-12</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,9 +118,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -532,98 +532,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -805,14 +807,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
@@ -822,13 +824,13 @@
         <v>77</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s" s="2">
         <v>78</v>
@@ -837,58 +839,58 @@
         <v>9</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>76</v>
@@ -903,7 +905,7 @@
         <v>80</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -915,7 +917,7 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
@@ -925,13 +927,13 @@
         <v>82</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s" s="2">
         <v>83</v>
@@ -945,50 +947,50 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF3" t="s" s="2">
         <v>86</v>
@@ -1000,10 +1002,10 @@
         <v>82</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="s" s="2">
         <v>87</v>
@@ -1018,7 +1020,7 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
@@ -1028,19 +1030,19 @@
         <v>76</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" t="s" s="2">
         <v>89</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
         <v>90</v>
@@ -1048,38 +1050,38 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB4" t="s" s="2">
         <v>91</v>
@@ -1088,7 +1090,7 @@
         <v>92</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="s" s="2">
         <v>93</v>
@@ -1103,13 +1105,13 @@
         <v>77</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -1121,7 +1123,7 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
@@ -1131,13 +1133,13 @@
         <v>82</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>96</v>
@@ -1153,50 +1155,50 @@
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
         <v>3</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>95</v>
@@ -1208,10 +1210,10 @@
         <v>82</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>100</v>
@@ -1226,7 +1228,7 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -1236,13 +1238,13 @@
         <v>82</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
         <v>102</v>
@@ -1256,50 +1258,50 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>101</v>
@@ -1311,7 +1313,7 @@
         <v>82</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>105</v>
